--- a/experimento_rev02.xlsx
+++ b/experimento_rev02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\OneDrive - Concremat Engenharia e Tecnologia\Projetos\PLISP\PD\app_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F9838C-1470-46FE-AC0E-78F6089078CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22D7CFE-30EB-4EE2-9701-843A8A8D5E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,18 +89,6 @@
     <t>Cenário com melhorias. Modo de baixa ou alta capacidade a depender da variável "Modo"</t>
   </si>
   <si>
-    <t>10% menos atrasos</t>
-  </si>
-  <si>
-    <t>10% mais atrasos</t>
-  </si>
-  <si>
-    <t>10% mais frequência/espaço</t>
-  </si>
-  <si>
-    <t>10% menos frequência/espaço</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -120,6 +108,18 @@
   </si>
   <si>
     <t>10% mais risco de perdas</t>
+  </si>
+  <si>
+    <t>30% menos atrasos</t>
+  </si>
+  <si>
+    <t>30% mais atrasos</t>
+  </si>
+  <si>
+    <t>30% mais frequência/espaço</t>
+  </si>
+  <si>
+    <t>30% menos frequência/espaço</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
         <v>-1</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1334,13 +1334,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="5">
-        <v>-0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1352,19 +1352,19 @@
         <v>0</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="5">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="4">
         <v>-1</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1402,7 +1402,7 @@
         <v>-1</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1428,33 +1428,33 @@
         <v>0</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="5">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="4">
         <v>-1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>16</v>
+      <c r="B14" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1466,22 +1466,22 @@
         <v>0</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C16" s="4">
         <v>-1</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1489,13 +1489,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" s="4">
         <v>1</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,33 +1507,33 @@
         <v>0</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4">
         <v>-1</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1545,19 +1545,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
-      <c r="B22" s="4" t="s">
-        <v>19</v>
+      <c r="B22" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C22" s="4">
         <v>-1</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -1571,7 +1571,7 @@
         <v>-1</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
